--- a/ParkingViolationPortal_TestCases.xlsx
+++ b/ParkingViolationPortal_TestCases.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus TUF F16\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus TUF F16\parking-violation-qa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26070C1B-544A-4E97-AEA5-FD4E6FC6936A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960AB78B-75DB-4EE1-BFA4-FD6EC902E895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="300">
   <si>
     <t>PARKING VIOLATION PORTAL — QA TEST SUMMARY</t>
   </si>
@@ -755,9 +755,6 @@
   </si>
   <si>
     <t>fine_breakdown identik dengan snapshot saat violation dibuat</t>
-  </si>
-  <si>
-    <t>TC-042</t>
   </si>
   <si>
     <t>Officer tidak bisa akses /transactions</t>
@@ -2007,44 +2004,52 @@
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -2201,7 +2206,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2239,26 +2244,6 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2274,9 +2259,6 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2285,6 +2267,26 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2597,80 +2599,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="14"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="25"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="14"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="25"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="14"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="25"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="14"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="25"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="14"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="25"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="14"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="25"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -2860,57 +2862,57 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="14"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="25"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="19" t="s">
+      <c r="B23" s="25"/>
+      <c r="C23" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="14"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="25"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="19" t="s">
+      <c r="B24" s="25"/>
+      <c r="C24" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="14"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="25"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="19" t="s">
+      <c r="B25" s="25"/>
+      <c r="C25" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="14"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="25"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="19" t="s">
+      <c r="B26" s="25"/>
+      <c r="C26" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="14"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -2957,22 +2959,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
@@ -3019,7 +3021,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="18" t="s">
         <v>53</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -3051,15 +3053,15 @@
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="M3" s="27" t="s">
-        <v>260</v>
+        <v>256</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N3" s="5"/>
     </row>
     <row r="4" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="18" t="s">
         <v>63</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -3091,15 +3093,15 @@
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="M4" s="27" t="s">
-        <v>260</v>
+        <v>257</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N4" s="3"/>
     </row>
     <row r="5" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="18" t="s">
         <v>69</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -3130,16 +3132,16 @@
         <v>74</v>
       </c>
       <c r="K5" s="5"/>
-      <c r="L5" s="25" t="s">
+      <c r="L5" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="M5" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="M5" s="27" t="s">
-        <v>260</v>
-      </c>
       <c r="N5" s="5"/>
     </row>
     <row r="6" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="18" t="s">
         <v>75</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -3170,16 +3172,16 @@
         <v>79</v>
       </c>
       <c r="K6" s="3"/>
-      <c r="L6" s="25" t="s">
+      <c r="L6" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="M6" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="M6" s="27" t="s">
-        <v>260</v>
-      </c>
       <c r="N6" s="3"/>
     </row>
     <row r="7" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="18" t="s">
         <v>80</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -3210,16 +3212,16 @@
         <v>85</v>
       </c>
       <c r="K7" s="5"/>
-      <c r="L7" s="25" t="s">
-        <v>261</v>
-      </c>
-      <c r="M7" s="27" t="s">
+      <c r="L7" s="13" t="s">
         <v>260</v>
       </c>
+      <c r="M7" s="15" t="s">
+        <v>259</v>
+      </c>
       <c r="N7" s="5"/>
     </row>
     <row r="8" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="18" t="s">
         <v>86</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -3250,16 +3252,16 @@
         <v>85</v>
       </c>
       <c r="K8" s="3"/>
-      <c r="L8" s="26" t="s">
-        <v>261</v>
-      </c>
-      <c r="M8" s="27" t="s">
+      <c r="L8" s="14" t="s">
         <v>260</v>
       </c>
+      <c r="M8" s="15" t="s">
+        <v>259</v>
+      </c>
       <c r="N8" s="3"/>
     </row>
     <row r="9" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="18" t="s">
         <v>90</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -3290,16 +3292,16 @@
         <v>97</v>
       </c>
       <c r="K9" s="5"/>
-      <c r="L9" s="28" t="s">
-        <v>262</v>
-      </c>
-      <c r="M9" s="27" t="s">
-        <v>260</v>
+      <c r="L9" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N9" s="5"/>
     </row>
     <row r="10" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="18" t="s">
         <v>98</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -3330,23 +3332,23 @@
         <v>103</v>
       </c>
       <c r="K10" s="3"/>
-      <c r="L10" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="M10" s="27" t="s">
-        <v>260</v>
+      <c r="L10" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N10" s="3"/>
     </row>
     <row r="11" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="18" t="s">
         <v>104</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="25" t="s">
-        <v>264</v>
+      <c r="C11" s="13" t="s">
+        <v>263</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>105</v>
@@ -3363,23 +3365,23 @@
       <c r="H11" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="I11" s="25" t="s">
-        <v>265</v>
+      <c r="I11" s="13" t="s">
+        <v>264</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>107</v>
       </c>
       <c r="K11" s="5"/>
-      <c r="L11" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="M11" s="27" t="s">
-        <v>260</v>
+      <c r="L11" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N11" s="5"/>
     </row>
     <row r="12" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="18" t="s">
         <v>108</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -3403,23 +3405,23 @@
       <c r="H12" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="I12" s="26" t="s">
-        <v>267</v>
+      <c r="I12" s="14" t="s">
+        <v>266</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>111</v>
       </c>
       <c r="K12" s="3"/>
-      <c r="L12" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="M12" s="27" t="s">
-        <v>260</v>
+      <c r="L12" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N12" s="3"/>
     </row>
     <row r="13" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="18" t="s">
         <v>112</v>
       </c>
       <c r="B13" s="5" t="s">
@@ -3440,26 +3442,26 @@
       <c r="G13" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="H13" s="25" t="s">
+      <c r="H13" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="I13" s="25" t="s">
+      <c r="I13" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="J13" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="J13" s="25" t="s">
+      <c r="K13" s="5"/>
+      <c r="L13" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="K13" s="5"/>
-      <c r="L13" s="25" t="s">
-        <v>271</v>
-      </c>
-      <c r="M13" s="27" t="s">
-        <v>260</v>
+      <c r="M13" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N13" s="5"/>
     </row>
     <row r="14" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="18" t="s">
         <v>116</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -3483,23 +3485,23 @@
       <c r="H14" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I14" s="26" t="s">
+      <c r="I14" s="14" t="s">
         <v>120</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>121</v>
       </c>
       <c r="K14" s="3"/>
-      <c r="L14" s="26" t="s">
-        <v>272</v>
-      </c>
-      <c r="M14" s="27" t="s">
-        <v>260</v>
+      <c r="L14" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N14" s="3"/>
     </row>
     <row r="15" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="18" t="s">
         <v>122</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -3530,25 +3532,25 @@
         <v>127</v>
       </c>
       <c r="K15" s="5"/>
-      <c r="L15" s="28" t="s">
-        <v>273</v>
-      </c>
-      <c r="M15" s="27" t="s">
-        <v>260</v>
+      <c r="L15" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N15" s="5"/>
     </row>
     <row r="16" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="13" t="s">
         <v>91</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="13" t="s">
         <v>133</v>
       </c>
       <c r="E16" s="8" t="s">
@@ -3563,27 +3565,27 @@
       <c r="H16" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="I16" s="25" t="s">
-        <v>274</v>
+      <c r="I16" s="13" t="s">
+        <v>273</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="K16" s="25" t="s">
-        <v>278</v>
-      </c>
-      <c r="L16" s="25" t="s">
-        <v>275</v>
-      </c>
-      <c r="M16" s="32" t="s">
+      <c r="K16" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="M16" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="N16" s="25" t="s">
-        <v>253</v>
+      <c r="N16" s="13" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="18" t="s">
         <v>131</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -3613,17 +3615,17 @@
       <c r="J17" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="K17" s="25"/>
-      <c r="L17" s="26" t="s">
-        <v>279</v>
-      </c>
-      <c r="M17" s="27" t="s">
-        <v>260</v>
+      <c r="K17" s="13"/>
+      <c r="L17" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="M17" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N17" s="3"/>
     </row>
     <row r="18" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="31" t="s">
+      <c r="A18" s="18" t="s">
         <v>135</v>
       </c>
       <c r="B18" s="5" t="s">
@@ -3654,26 +3656,26 @@
         <v>144</v>
       </c>
       <c r="K18" s="5"/>
-      <c r="L18" s="25" t="s">
-        <v>279</v>
-      </c>
-      <c r="M18" s="27" t="s">
-        <v>260</v>
+      <c r="L18" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N18" s="5"/>
     </row>
     <row r="19" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="D19" s="13" t="s">
         <v>295</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>296</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>72</v>
@@ -3684,30 +3686,30 @@
       <c r="G19" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="H19" s="25" t="s">
+      <c r="H19" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="I19" s="25" t="s">
-        <v>297</v>
+      <c r="I19" s="13" t="s">
+        <v>296</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="K19" s="25" t="s">
-        <v>298</v>
-      </c>
-      <c r="L19" s="25" t="s">
-        <v>298</v>
-      </c>
-      <c r="M19" s="32" t="s">
+      <c r="K19" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="L19" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="M19" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="N19" s="25" t="s">
-        <v>254</v>
+      <c r="N19" s="13" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="18" t="s">
         <v>145</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -3731,23 +3733,23 @@
       <c r="H20" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I20" s="26" t="s">
+      <c r="I20" s="14" t="s">
         <v>148</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>149</v>
       </c>
       <c r="K20" s="3"/>
-      <c r="L20" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="M20" s="27" t="s">
-        <v>260</v>
+      <c r="L20" s="14" t="s">
+        <v>279</v>
+      </c>
+      <c r="M20" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N20" s="3"/>
     </row>
     <row r="21" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="18" t="s">
         <v>150</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -3778,18 +3780,18 @@
         <v>156</v>
       </c>
       <c r="K21" s="5"/>
-      <c r="L21" s="25" t="s">
-        <v>281</v>
-      </c>
-      <c r="M21" s="27" t="s">
-        <v>260</v>
+      <c r="L21" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="M21" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N21" s="5" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="18" t="s">
         <v>158</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -3820,18 +3822,18 @@
         <v>163</v>
       </c>
       <c r="K22" s="3"/>
-      <c r="L22" s="26" t="s">
-        <v>281</v>
-      </c>
-      <c r="M22" s="27" t="s">
-        <v>260</v>
+      <c r="L22" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="M22" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="18" t="s">
         <v>164</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -3862,16 +3864,16 @@
         <v>170</v>
       </c>
       <c r="K23" s="3"/>
-      <c r="L23" s="26" t="s">
-        <v>282</v>
-      </c>
-      <c r="M23" s="27" t="s">
-        <v>260</v>
+      <c r="L23" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="M23" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N23" s="3"/>
     </row>
     <row r="24" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="18" t="s">
         <v>165</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -3898,20 +3900,20 @@
       <c r="I24" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="J24" s="26" t="s">
+      <c r="J24" s="14" t="s">
         <v>176</v>
       </c>
       <c r="K24" s="3"/>
-      <c r="L24" s="33" t="s">
-        <v>283</v>
-      </c>
-      <c r="M24" s="27" t="s">
-        <v>260</v>
+      <c r="L24" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="M24" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N24" s="3"/>
     </row>
     <row r="25" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="18" t="s">
         <v>171</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -3942,16 +3944,16 @@
         <v>183</v>
       </c>
       <c r="K25" s="5"/>
-      <c r="L25" s="28" t="s">
-        <v>284</v>
-      </c>
-      <c r="M25" s="27" t="s">
-        <v>260</v>
+      <c r="L25" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="M25" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N25" s="5"/>
     </row>
     <row r="26" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="18" t="s">
         <v>172</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -3982,16 +3984,16 @@
         <v>188</v>
       </c>
       <c r="K26" s="3"/>
-      <c r="L26" s="26" t="s">
-        <v>285</v>
-      </c>
-      <c r="M26" s="27" t="s">
-        <v>260</v>
+      <c r="L26" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="M26" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N26" s="3"/>
     </row>
     <row r="27" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="18" t="s">
         <v>177</v>
       </c>
       <c r="B27" s="5" t="s">
@@ -4022,16 +4024,16 @@
         <v>199</v>
       </c>
       <c r="K27" s="5"/>
-      <c r="L27" s="28" t="s">
-        <v>286</v>
-      </c>
-      <c r="M27" s="27" t="s">
-        <v>260</v>
+      <c r="L27" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="M27" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N27" s="5"/>
     </row>
     <row r="28" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="18" t="s">
         <v>184</v>
       </c>
       <c r="B28" s="5" t="s">
@@ -4062,16 +4064,16 @@
         <v>206</v>
       </c>
       <c r="K28" s="5"/>
-      <c r="L28" s="28" t="s">
-        <v>287</v>
-      </c>
-      <c r="M28" s="27" t="s">
-        <v>260</v>
+      <c r="L28" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="M28" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N28" s="5"/>
     </row>
     <row r="29" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="31" t="s">
+      <c r="A29" s="18" t="s">
         <v>189</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -4102,16 +4104,16 @@
         <v>130</v>
       </c>
       <c r="K29" s="3"/>
-      <c r="L29" s="26" t="s">
-        <v>288</v>
-      </c>
-      <c r="M29" s="27" t="s">
-        <v>260</v>
+      <c r="L29" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="M29" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N29" s="3"/>
     </row>
     <row r="30" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="31" t="s">
+      <c r="A30" s="18" t="s">
         <v>190</v>
       </c>
       <c r="B30" s="5" t="s">
@@ -4142,16 +4144,16 @@
         <v>215</v>
       </c>
       <c r="K30" s="5"/>
-      <c r="L30" s="28" t="s">
-        <v>289</v>
-      </c>
-      <c r="M30" s="27" t="s">
-        <v>260</v>
+      <c r="L30" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="M30" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N30" s="5"/>
     </row>
     <row r="31" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="31" t="s">
+      <c r="A31" s="18" t="s">
         <v>191</v>
       </c>
       <c r="B31" s="3" t="s">
@@ -4182,16 +4184,16 @@
         <v>219</v>
       </c>
       <c r="K31" s="3"/>
-      <c r="L31" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="M31" s="27" t="s">
-        <v>260</v>
+      <c r="L31" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="M31" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N31" s="3"/>
     </row>
     <row r="32" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="31" t="s">
+      <c r="A32" s="18" t="s">
         <v>192</v>
       </c>
       <c r="B32" s="5" t="s">
@@ -4222,16 +4224,16 @@
         <v>225</v>
       </c>
       <c r="K32" s="5"/>
-      <c r="L32" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="M32" s="27" t="s">
-        <v>260</v>
+      <c r="L32" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="M32" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N32" s="5"/>
     </row>
     <row r="33" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="18" t="s">
         <v>193</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -4262,26 +4264,26 @@
         <v>230</v>
       </c>
       <c r="K33" s="3"/>
-      <c r="L33" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="M33" s="27" t="s">
-        <v>260</v>
+      <c r="L33" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="M33" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N33" s="3"/>
     </row>
     <row r="34" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="18" t="s">
         <v>200</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>220</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>72</v>
@@ -4296,32 +4298,32 @@
         <v>101</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>130</v>
       </c>
       <c r="K34" s="3"/>
-      <c r="L34" s="26" t="s">
-        <v>288</v>
-      </c>
-      <c r="M34" s="27" t="s">
-        <v>260</v>
+      <c r="L34" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="M34" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N34" s="3"/>
     </row>
     <row r="35" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="18" t="s">
         <v>201</v>
       </c>
       <c r="B35" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="D35" s="5" t="s">
         <v>236</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>237</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>72</v>
@@ -4333,35 +4335,35 @@
         <v>59</v>
       </c>
       <c r="H35" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="I35" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="I35" s="5" t="s">
+      <c r="J35" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="J35" s="5" t="s">
+      <c r="K35" s="5"/>
+      <c r="L35" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="M35" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="N35" s="5"/>
+    </row>
+    <row r="36" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="K35" s="5"/>
-      <c r="L35" s="25" t="s">
-        <v>293</v>
-      </c>
-      <c r="M35" s="27" t="s">
-        <v>260</v>
-      </c>
-      <c r="N35" s="5"/>
-    </row>
-    <row r="36" spans="1:14" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>72</v>
@@ -4376,17 +4378,17 @@
         <v>129</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>130</v>
       </c>
       <c r="K36" s="3"/>
-      <c r="L36" s="26" t="s">
-        <v>288</v>
-      </c>
-      <c r="M36" s="27" t="s">
-        <v>260</v>
+      <c r="L36" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="M36" s="15" t="s">
+        <v>259</v>
       </c>
       <c r="N36" s="3"/>
     </row>
@@ -4430,33 +4432,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
+      <c r="A1" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
     </row>
     <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C2" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>247</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>248</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>44</v>
@@ -4465,13 +4467,13 @@
         <v>45</v>
       </c>
       <c r="G2" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>251</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>50</v>
@@ -4480,20 +4482,20 @@
         <v>51</v>
       </c>
       <c r="L2" s="7" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="18" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="31" t="s">
-        <v>253</v>
-      </c>
-      <c r="B3" s="30" t="s">
-        <v>231</v>
-      </c>
-      <c r="C3" s="29" t="s">
+      <c r="B3" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="13" t="s">
         <v>91</v>
       </c>
       <c r="E3" s="10" t="s">
@@ -4502,36 +4504,36 @@
       <c r="F3" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="25" t="s">
-        <v>274</v>
-      </c>
-      <c r="H3" s="25" t="s">
-        <v>294</v>
-      </c>
-      <c r="I3" s="25" t="s">
+      <c r="G3" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="L3" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="K3" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="L3" s="25" t="s">
-        <v>277</v>
-      </c>
     </row>
     <row r="4" spans="1:12" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="31" t="s">
-        <v>253</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>231</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>299</v>
-      </c>
-      <c r="D4" s="25" t="s">
+      <c r="A4" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>91</v>
       </c>
       <c r="E4" s="10" t="s">
@@ -4540,23 +4542,23 @@
       <c r="F4" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="25" t="s">
-        <v>300</v>
-      </c>
-      <c r="H4" s="25" t="s">
-        <v>279</v>
-      </c>
-      <c r="I4" s="25" t="s">
-        <v>298</v>
+      <c r="G4" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>297</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="L4" s="25" t="s">
-        <v>277</v>
+        <v>254</v>
+      </c>
+      <c r="L4" s="13" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
